--- a/49849_Intercuenca_Alto_Huallaga/_raw_reportes_xlsx/IDConfig_64952_completo.xlsx
+++ b/49849_Intercuenca_Alto_Huallaga/_raw_reportes_xlsx/IDConfig_64952_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R1360a8a917e2467f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Ra1687752c1cf4444"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,141 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     77.3680</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     62.1729</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     72.2955</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.2558</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     83.1268</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     71.6133</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     69.0547</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     77.3329</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     58.5129</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>

--- a/49849_Intercuenca_Alto_Huallaga/_raw_reportes_xlsx/IDConfig_64952_completo.xlsx
+++ b/49849_Intercuenca_Alto_Huallaga/_raw_reportes_xlsx/IDConfig_64952_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Ra1687752c1cf4444"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R5793bdd6043c4002"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,726 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     76.2696</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    101.2966</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     69.9453</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     67.4310</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     70.7839</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     76.1194</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     75.8922</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     86.2842</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     90.6802</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    128.5188</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.8490</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     80.0607</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     89.2769</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    178.6041</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     67.3480</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     75.8844</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     74.4107</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     95.1731</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    130.2216</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     74.9956</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     88.2847</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    129.7000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    152.8042</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    167.0291</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    163.5718</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.3664</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    101.6640</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     52.5835</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     58.5749</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     66.1225</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     75.3864</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    107.0812</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     76.6257</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     68.3807</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     61.3770</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     62.2148</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     51.3264</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     53.4002</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     50.7974</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     52.3495</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     53.6398</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     55.8749</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     58.3594</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     61.0036</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     70.2725</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    101.9398</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.6562</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     76.5524</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
@@ -279,7 +999,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     62.1729</x:v>
+        <x:v>     63.4591</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -294,7 +1014,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     72.2955</x:v>
+        <x:v>     73.7133</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -309,7 +1029,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    111.2558</x:v>
+        <x:v>    113.1293</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -324,7 +1044,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     83.1268</x:v>
+        <x:v>     84.6785</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -339,7 +1059,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     71.6133</x:v>
+        <x:v>     73.0227</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -369,7 +1089,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     77.3329</x:v>
+        <x:v>     77.9249</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -744,7 +1464,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    101.7163</x:v>
+        <x:v>    100.7075</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -759,7 +1479,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     70.7817</x:v>
+        <x:v>     70.7365</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1149,7 +1869,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    107.6209</x:v>
+        <x:v>    107.3143</x:v>
       </x:c>
     </x:row>
     <x:row>
